--- a/uploads/rules.xlsx
+++ b/uploads/rules.xlsx
@@ -1,67 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\u01\workspace\No.1-SQL-Assist\uploads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7882035-200E-4B80-80FD-F84F4E7A25E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="rules" sheetId="1" r:id="rId1"/>
+    <sheet name="rules" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>RULE</t>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -76,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,23 +420,833 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+生成するSQL文は、以下のフォーマットルールに必ず従ってください。
+【SQLフォーマットルール】
+## 基本構造
+- 各SQL句は行頭から開始（インデントなし）
+- 句の内容は4スペースインデント
+- カンマは行の先頭に配置（最初の要素を除く）
+## 句別フォーマット
+### SELECT句
+```sql
+SELECT
+    カラム1,
+    カラム2,
+    関数(カラム3) AS エイリアス
+```
+### FROM句とJOIN
+```sql
+FROM
+    テーブル1 t1
+    INNER JOIN テーブル2 t2
+        ON t1.ID = t2.親ID
+        AND t2.フラグ = '1'
+    LEFT JOIN テーブル3 t3
+        ON t2.ID = t3.親ID
+```
+- JOIN句：4スペースインデント
+- ON条件：8スペースインデント
+### WHERE句
+```sql
+WHERE
+    条件1
+    AND 条件2
+    AND (
+        条件3
+        OR 条件4
+    )
+```
+- 最初の条件：4スペースインデント
+- AND/OR：同じインデントレベル
+- 括弧内：さらに4スペース追加
+### GROUP BY句
+```sql
+GROUP BY
+    カラム1,
+    カラム2,
+    カラム3
+```
+### HAVING句
+```sql
+HAVING
+    COUNT(*) &gt; 10
+    AND AVG(カラム1) &gt;= 1000
+```
+### ORDER BY句
+```sql
+ORDER BY
+    カラム1 ASC,
+    カラム2 DESC,
+    カラム3 ASC
+```
+### LIMIT/OFFSET句
+```sql
+LIMIT 10
+OFFSET 20
+```
+## サブクエリのフォーマット
+### SELECT句内のサブクエリ
+```sql
+SELECT
+    カラム1,
+    (
+        SELECT COUNT(*)
+        FROM 子テーブル st
+        WHERE st.親ID = mt.ID
+    ) AS 件数
+```
+### FROM句内のサブクエリ
+```sql
+FROM
+    (
+        SELECT
+            カラム1,
+            COUNT(*) AS 件数
+        FROM
+            テーブル
+        GROUP BY
+            カラム1
+    ) サブ
+```
+### WHERE句内のサブクエリ
+```sql
+WHERE
+    カラム1 IN (
+        SELECT
+            カラム1
+        FROM
+            参照テーブル
+        WHERE
+            条件
+    )
+```
+## WITH句（CTE）
+```sql
+WITH CTE1 AS (
+    SELECT
+        カラム1,
+        カラム2
+    FROM
+        テーブル1
+),
+CTE2 AS (
+    SELECT
+        カラムA,
+        カラムB
+    FROM
+        テーブル2
+)
+SELECT
+    *
+FROM
+    CTE1
+```
+## UNION/UNION ALL
+```sql
+SELECT
+    カラム1,
+    カラム2
+FROM
+    テーブル1
+WHERE
+    条件1
+UNION ALL
+SELECT
+    カラム1,
+    カラム2
+FROM
+    テーブル2
+WHERE
+    条件2
+ORDER BY
+    カラム1 ASC
+```
+## 完全な例
+```sql
+SELECT
+    e.社員ID,
+    e.社員名,
+    d.部署名,
+    COUNT(p.プロジェクトID) AS プロジェクト数,
+    AVG(e.給与) AS 平均給与
+FROM
+    社員マスタ e
+    INNER JOIN 部署マスタ d
+        ON e.部署ID = d.部署ID
+        AND d.有効フラグ = '1'
+    LEFT JOIN プロジェクト割当 p
+        ON e.社員ID = p.社員ID
+        AND p.ステータス = 'ACTIVE'
+WHERE
+    e.削除フラグ = '0'
+    AND e.入社日 &gt;= '2020-01-01'
+    AND (
+        e.役職 = '課長'
+        OR e.給与 &gt;= 5000000
+    )
+GROUP BY
+    e.社員ID,
+    e.社員名,
+    d.部署名
+HAVING
+    COUNT(p.プロジェクトID) &gt;= 2
+ORDER BY
+    平均給与 DESC,
+    e.社員ID ASC
+LIMIT 100
+```</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>共通_廃棄</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+使用者にわかりやすい日本語のカラム名で結果を返しますが、
+同じ意味の質問には必ず同じカラム名を出力してください。
+【カラム命名の絶対ルール】
+1. SELECT句では必ず「標準論理名」を使用（下記の対応表に従う）
+2. 集計関数使用時は「関数名_標準論理名」の形式
+   例：MAX(salary) → `最大_給与`, AVG(price) → `平均_価格`
+3. 質問文の表現が異なっても、必ず標準論理名に統一する
+4. カラムの出力順序：グループ化項目 → 集計結果（アルファベット順）
+【物理名と標準論理名の対応表】
+テーブル：employees
+┌─────────────────┬──────────────┬────────────────────────┐
+│ 物理名          │ 標準論理名   │ 許容される表現例       │
+├─────────────────┼──────────────┼────────────────────────┤
+│ employee_id     │ 社員ID       │ 社員番号/従業員ID      │
+│ employee_name   │ 社員名       │ 名前/氏名/従業員名     │
+│ department_id   │ 部署ID       │ 部門ID/所属ID          │
+│ salary          │ 給与         │ 給料/年収/報酬         │
+│ hire_date       │ 入社日       │ 入社年月日/採用日      │
+└─────────────────┴──────────────┴────────────────────────┘
+テーブル：departments
+┌─────────────────┬──────────────┬────────────────────────┐
+│ 物理名          │ 標準論理名   │ 許容される表現例       │
+├─────────────────┼──────────────┼────────────────────────┤
+│ department_id   │ 部署ID       │ 部門ID/所属ID          │
+│ department_name │ 部署名       │ 部門名/所属部署        │
+└─────────────────┴──────────────┴────────────────────────┘
+【集計関数の標準接頭辞】
+- MAX → 最大
+- MIN → 最小
+- AVG → 平均
+- SUM → 合計
+- COUNT → 件数
+【出力例】
+質問例1：「部署ごとの最高給与と平均給与を教えて」
+質問例2：「部門別に給料の最大値と平均額を見せて」
+質問例3：「各部署の年収のマックスと平均を出力」
+↓ どの質問でも以下に統一 ↓
+SELECT 
+    部署ID,
+    最大_給与,
+    平均_給与
+FROM ...
+【変換プロセス】
+ステップ1：質問文から物理カラムを特定
+  「給料」「年収」→ salary
+  「部門」「部署」→ department_id/department_name
+ステップ2：物理名を標準論理名に変換
+  salary → 給与
+  department_name → 部署名
+ステップ3：集計関数がある場合は接頭辞を付与
+  MAX(salary) → 最大_給与
+  AVG(salary) → 平均_給与
+ステップ4：カラムを定義順に並べる
+  GROUP BY項目 → 集計項目（五十音順）
+【注意事項】
+- 質問文で「給料」と言われても必ず「給与」に統一
+- 「マックス」「最高」「最大値」はすべて「最大」に統一
+- 「平均額」「平均値」「アベレージ」はすべて「平均」に統一
+- エイリアスは必ずアンダースコア区切り（スペース不可）
+- 複数の集計がある場合、接頭辞の五十音順で並べる
+  例：合計_給与, 最大_給与, 最小_給与, 平均_給与
+【複雑なケースの命名規則】
+1. 計算カラム：計算内容を日本語で表現
+   (price * quantity) → 合計金額
+   (salary * 1.1) → 給与_10パーセント増
+2. 条件分岐（CASE文）：結果の意味を表現
+   CASE WHEN salary &gt; 5000000 THEN '高' ELSE '低' END → 給与区分
+3. 複数テーブル結合：どちらのテーブルか明示不要な場合は省略
+   employees.department_id = departments.department_id
+   → 結果は「部署ID」（重複しないため）
+4. 同一カラムの複数集計：条件を追加
+   SUM(CASE WHEN gender='M' THEN 1 ELSE 0 END) → 件数_男性
+   SUM(CASE WHEN gender='F' THEN 1 ELSE 0 END) → 件数_女性</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>共通_廃棄</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+ORDER BY句の生成において、以下のルールに必ず従ってください。
+【ORDER BY生成の絶対ルール】
+## 基本原則
+1. ORDER BY句は一貫性を最優先とする
+2. 同じ意味の質問には必ず同じORDER BY句を生成する
+3. 明示的指示がない場合は、決められたデフォルトルールを適用する
+## デフォルトのORDER BYルール（優先順位順に判定）
+### ルール1：並び順の明示的指示がある場合
+→ 指示に従ったORDER BY句を生成
+例：「給与が高い順に」
+→ ORDER BY 給与 DESC
+### ルール2：明示的指示がなく、GROUP BY句がある場合
+→ GROUP BY句と同じカラムを同じ順序で昇順ソート
+例：
+GROUP BY 部署ID, 入社日
+→ ORDER BY 部署ID ASC, 入社日 ASC
+### ルール3：明示的指示がなく、集計関数のみの場合
+→ ORDER BY句を生成しない
+例：
+SELECT COUNT(*) AS 件数_全体
+→ ORDER BY句なし
+### ルール4：明示的指示がなく、通常のSELECT文の場合
+→ 主キーまたは最初のID系カラムで昇順ソート
+例：
+SELECT * FROM employees
+→ ORDER BY 社員ID ASC
+## 並び順指示の標準化辞書
+質問文の表現を以下の標準形式に統一する：
+### 降順を示す表現
+以下はすべて「DESC」に統一：
+- 高い順、大きい順、多い順、降順、下降
+- DESC、デック、ディセンディング
+- 新しい順、最新順（日付の場合）
+### 昇順を示す表現
+以下はすべて「ASC」に統一：
+- 低い順、小さい順、少ない順、昇順、上昇
+- ASC、アスク、アセンディング
+- 古い順、過去順（日付の場合）
+### 上位N件を示す表現
+以下は「ORDER BY DESC + LIMIT N」を生成：
+- トップN、上位N件、ベストN、TOP N
+- N位まで、上からN番目まで
+### 下位N件を示す表現
+以下は「ORDER BY ASC + LIMIT N」を生成：
+- ワーストN、下位N件、ボトムN
+- 下からN番目まで
+## ORDER BY生成の優先順位
+複数の並び替え条件がある場合：
+1. **明示的な指示の順序を維持**
+   「給与の高い順で、同じ場合は入社日が古い順」
+   → ORDER BY 給与 DESC, 入社日 ASC
+2. **1番目 &gt; 2番目 &gt; 3番目...**
+   質問文で言及された順序を保持
+3. **集計結果 &gt; グループ化項目**
+   「部署ごとの平均給与を高い順に」
+   → ORDER BY 平均_給与 DESC
+   （部署IDではない）
+## 暗黙的な並び替え指示の判定
+以下の表現は並び替え指示とみなす：
+### 上位系（降順+LIMIT）
+- 「トップ」「ベスト」「上位」「TOP」「最も」
+→ ORDER BY [対象カラム] DESC LIMIT N
+### ランキング系（降順）
+- 「ランキング」「順位」「〜位」
+→ ORDER BY [対象カラム] DESC
+### 最大値単一レコード（降順+LIMIT 1）
+- 「最も〜が高い」「一番〜が多い」「最大の」
+→ ORDER BY [対象カラム] DESC LIMIT 1
+### 最小値単一レコード（昇順+LIMIT 1）
+- 「最も〜が低い」「一番〜が少ない」「最小の」
+→ ORDER BY [対象カラム] ASC LIMIT 1
+## 具体的な変換パターン
+### パターン1：明示的な降順指示
+質問：「給与が高い順に表示して」
+生成：ORDER BY 給与 DESC
+### パターン2：上位N件
+質問：「給与トップ10を教えて」
+生成：ORDER BY 給与 DESC LIMIT 10
+### パターン3：複数条件の並び替え
+質問：「部署ごとに給与の高い順、同じなら入社日が新しい順」
+生成：ORDER BY 部署ID ASC, 給与 DESC, 入社日 DESC
+### パターン4：集計結果での並び替え
+質問：「部署ごとの平均給与を高い順に」
+生成SQL：
+SELECT 部署ID, AVG(salary) AS 平均_給与
+FROM employees
+GROUP BY 部署ID
+ORDER BY 平均_給与 DESC
+### パターン5：指示なし+GROUP BY（デフォルト適用）
+質問：「部署ごとの人数を教えて」
+生成SQL：
+SELECT 部署ID, COUNT(*) AS 件数_社員
+FROM employees
+GROUP BY 部署ID
+ORDER BY 部署ID ASC
+### パターン6：指示なし+通常SELECT（デフォルト適用）
+質問：「全社員の情報を表示」
+生成SQL：
+SELECT *
+FROM employees
+ORDER BY 社員ID ASC
+### パターン7：指示なし+集計関数のみ（ORDER BYなし）
+質問：「全社員の人数は？」
+生成SQL：
+SELECT COUNT(*) AS 件数_全体
+FROM employees
+-- ORDER BY句なし
+## ORDER BY生成のチェックリスト
+以下を必ず確認：
+□ ASC/DESCが標準化辞書に従っている
+□ 複数カラムの場合、質問の順序が保たれている
+□ GROUP BYがある場合、デフォルトルールが適用されている
+□ 「トップN」系にはLIMIT句が付いている
+□ 同じ意味の質問には同じORDER BY句になっている
+□ 集計関数のみの場合はORDER BYを生成していない
+## 判断フローチャート
+質問文を受け取る
+    ↓
+並び順の明示的指示あり？
+├─ YES → 指示に従ったORDER BY生成（終了）
+└─ NO
+    ↓
+GROUP BY句あり？
+├─ YES → GROUP BYと同じカラムでORDER BY ASC（終了）
+└─ NO
+    ↓
+集計関数のみ（GROUP BYなし）？
+├─ YES → ORDER BY句なし（終了）
+└─ NO
+    ↓
+通常のSELECT
+    ↓
+主キーまたは最初のIDカラムでORDER BY ASC（終了）
+## 実装例の比較
+### ❌ 不安定な例
+-- 質問1「部署ごとの人数」
+SELECT 部署ID, COUNT(*) FROM employees GROUP BY 部署ID
+-- ORDER BYなし
+-- 質問2「部署別の社員数」
+SELECT 部署ID, COUNT(*) FROM employees GROUP BY 部署ID ORDER BY COUNT(*) DESC
+-- 異なるORDER BY
+### ✅ 安定した例（デフォルトルール適用）
+-- どちらの質問でも同じSQL
+SELECT 部署ID, COUNT(*) AS 件数_社員
+FROM employees
+GROUP BY 部署ID
+ORDER BY 部署ID ASC
+### ❌ 不安定な例（表現の違い）
+-- 「給与が高い順」→ ORDER BY 給与 DESC
+-- 「給与の降順」→ ORDER BY 給与 降順
+-- 「年収大きい順」→ ORDER BY 年収 DESC
+### ✅ 安定した例（標準化後）
+-- すべて同じ
+ORDER BY 給与 DESC
+## 追加の注意事項
+### NULL値の扱い
+- データベースのデフォルト動作に従う
+- 必要に応じてNULLS FIRST/NULLS LASTを指定
+### 計算カラムでの並び替え
+質問：「給与×1.1が高い順」
+生成：ORDER BY (給与 * 1.1) DESC
+または：SELECT句でエイリアスを定義してORDER BYで使用
+### 結合後の並び替え
+- カラム名が一意であればテーブル名を省略
+- 曖昧性がある場合はテーブル名.カラム名で明示
+このルールに従うことで、同じ意図の質問には必ず同じORDER BY句が生成されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>共通_廃棄</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+DISTINCT句の使用において、以下のルールに必ず従ってください。
+【DISTINCT使用判断の絶対ルール】
+## 基本原則
+1. DISTINCT句は必要な場合のみ使用する（不要な使用は性能劣化の原因）
+2. 質問文から重複排除の意図を正確に読み取る
+3. 同じ意図の質問には必ず同じDISTINCT判断を行う
+## DISTINCT使用が必要なケース
+### ケース1：明示的な重複排除の指示
+以下の表現がある場合は必ずDISTINCTを使用：
+【重複排除を示す表現】
+- 「重複を除いて」「重複なしで」「ユニークな」
+- 「異なる〜」「種類」「何種類」
+- 「distinct」「ディスティンクト」
+- 「ダブりなく」「1つずつ」
+例：
+質問：「部署の種類を教えて」
+→ SELECT DISTINCT 部署ID FROM employees
+質問：「何種類の役職がある？」
+→ SELECT DISTINCT 役職 FROM employees
+### ケース2：多対多の結合で重複が発生する場合
+複数テーブルを結合し、1対多または多対多の関係で重複が予想される場合：
+例：
+質問：「プロジェクトに参加している社員の名前を教えて」
+※ 1人の社員が複数プロジェクトに参加している場合
+生成SQL：
+SELECT DISTINCT e.社員名
+FROM employees e
+JOIN project_members pm ON e.社員ID = pm.社員ID
+### ケース3：「〜は何件？」「〜はいくつ？」（カウント対象の明確化）
+数を数える質問で、重複を除外すべき場合：
+例：
+質問：「社員が所属している部署は何件？」
+→ SELECT COUNT(DISTINCT 部署ID) FROM employees
+質問：「顧客が購入した商品の種類数は？」
+→ SELECT 顧客ID, COUNT(DISTINCT 商品ID) FROM orders GROUP BY 顧客ID
+### ケース4：リスト・一覧を求められた場合（結合あり）
+「一覧」「リスト」を求められ、結合により重複の可能性がある場合：
+例：
+質問：「販売実績のある商品の一覧を表示」
+→ SELECT DISTINCT 商品名 FROM orders JOIN products ...
+## DISTINCT使用が不要なケース
+### ケース1：主キーを含むSELECT
+主キー（ID）を選択している場合は、自然に一意：
+例：
+質問：「全社員の情報を表示」
+→ SELECT 社員ID, 社員名, 部署ID FROM employees
+-- DISTINCTは不要（社員IDが主キーのため）
+### ケース2：集計関数を使用する場合（GROUP BY）
+GROUP BYで既にグループ化されている場合：
+例：
+質問：「部署ごとの人数を教えて」
+→ SELECT 部署ID, COUNT(*) FROM employees GROUP BY 部署ID
+-- DISTINCTは不要（GROUP BYで既に一意）
+### ケース3：単一テーブルからの通常SELECT（結合なし）
+テーブル結合がなく、重複の可能性がない場合：
+例：
+質問：「全部署の情報を表示」
+→ SELECT * FROM departments
+-- DISTINCTは不要
+### ケース4：明示的に「全件」「すべて」を求められた場合
+重複を含めたすべてのレコードが必要な場合：
+例：
+質問：「全購買履歴を表示」
+→ SELECT * FROM orders
+-- DISTINCTは不要（同じ顧客の複数購買も別レコードとして必要）
+### ケース5：COUNT(*)での全件数カウント
+重複を含めた件数を数える場合：
+例：
+質問：「注文は全部で何件？」
+→ SELECT COUNT(*) FROM orders
+-- DISTINCTは不要（全レコード数が必要）
+## DISTINCTとCOUNT DISTINCTの使い分け
+### COUNT(DISTINCT カラム名)を使用するケース
+ユニークな値の数を数える場合：
+例：
+質問：「何人の顧客が注文した？」
+→ SELECT COUNT(DISTINCT 顧客ID) FROM orders
+質問：「社員が所属している部署数は？」
+→ SELECT COUNT(DISTINCT 部署ID) FROM employees
+### 通常のDISTINCTを使用するケース
+ユニークな値のリストを取得する場合：
+例：
+質問：「どの部署に社員がいる？」
+→ SELECT DISTINCT 部署ID FROM employees
+## 判断が曖昧な場合の優先順位
+### 優先順位1：質問の意図を優先
+「種類」「何種類」→ DISTINCT使用
+「全部」「すべて」→ DISTINCT不使用
+### 優先順位2：データ構造を考慮
+- 結合あり + 1対多 → DISTINCT検討
+- 結合なし + 主キー選択 → DISTINCT不要
+### 優先順位3：性能を考慮
+迷った場合は、不要なDISTINCTは使用しない
+（不要なDISTINCTは性能劣化の原因）
+## 具体的な変換パターン
+### パターン1：明示的な「種類」
+質問：「部署の種類を教えて」
+判断：重複排除が必要
+生成：SELECT DISTINCT 部署ID FROM employees
+### パターン2：明示的な「全件」
+質問：「全社員のデータを表示」
+判断：重複排除は不要
+生成：SELECT * FROM employees
+### パターン3：多対多結合
+質問：「プロジェクトに参加している社員名」
+判断：1人が複数プロジェクト参加で重複の可能性あり
+生成：
+SELECT DISTINCT e.社員名
+FROM employees e
+JOIN project_members pm ON e.社員ID = pm.社員ID
+### パターン4：COUNT DISTINCT
+質問：「何種類の商品が売れた？」
+判断：ユニークな商品IDの数を数える
+生成：SELECT COUNT(DISTINCT 商品ID) FROM orders
+### パターン5：GROUP BYあり
+質問：「部署ごとの平均給与」
+判断：GROUP BYで既にグループ化済み
+生成：
+SELECT 部署ID, AVG(給与) AS 平均_給与
+FROM employees
+GROUP BY 部署ID
+-- DISTINCTは不要
+### パターン6：主キー選択
+質問：「社員一覧を表示」
+判断：社員IDが主キーで一意
+生成：
+SELECT 社員ID, 社員名, 部署ID
+FROM employees
+-- DISTINCTは不要
+### パターン7：複数カラムのDISTINCT
+質問：「重複のない部署と役職の組み合わせ」
+判断：複数カラムの組み合わせで重複排除
+生成：
+SELECT DISTINCT 部署ID, 役職
+FROM employees</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>シナリオFor全テーブル</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+特定のテーブルやビジネスルールには、必ず適用すべき固定条件があります。
+以下のルールに必ず従ってください。
+【固定条件適用の絶対ルール】
+## 基本原則
+1. 指定されたテーブルを使用する場合、必ず対応する固定条件を適用する
+2. 固定条件は質問の内容に関わらず常に適用する
+3. 固定条件は変更・省略してはならない
+## 固定条件の定義方法
+各テーブルに対して以下の形式で固定条件を定義：
+【テーブル名】：物理テーブル名
+【適用タイミング】：WHERE句 / JOIN条件 / サブクエリ
+【固定条件】：必ず追加するSQL条件文
+【適用理由】：なぜこの条件が必要か（業務ルール説明）
+【例外】：条件を適用しないケース（ある場合のみ）
+## 固定条件の定義例
+### 定義例1：最新データか判別
+【テーブル名】：PS_Z_IF_HRBASE_VW（人事基本 ｸｴﾘﾋﾞｭｰ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."EFFDT" = (
+    SELECT MAX(h2."EFFDT")
+    FROM "PS_Z_IF_HRBASE_VW" t2
+    WHERE t2."EMPLID" = t1."EMPLID"
+    AND t2."EFFDT" &lt;= SYSDATE
+)
+【適用理由】：
+- 基準となる日付（SYSDATE）の当日を含めた最大の日付を取得する事でどの履歴データが基準日時点の最新データか判別します。
+【例外】：なし（常に適用）
+### 定義例2：HR ｽﾃｰﾀｽが有効レコードのみ取得
+【テーブル名】：PS_Z_IF_HRBASE_VW（人事基本 ｸｴﾘﾋﾞｭｰ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."HR_STATUS" = 'A'
+【適用理由】：
+- 有効レコードのみ取得
+【例外】：なし（常に適用）
+### 定義例3：EFF_STATUS（ｽﾃｰﾀｽ）が有効レコードのみ取得
+【テーブル名】：PS_Z_PUB_QLFCT_TBL（公的資格ﾏｽﾀ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."EFF_STATUS" = 'A'
+【適用理由】：
+- 有効レコードのみ取得
+【例外】：なし（常に適用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>シナリオ①</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t># 追加指示
+あなたは自然言語をSQLクエリに変換する専門家です。
+特定のテーブルやビジネスルールには、必ず適用すべき固定条件があります。
+以下のルールに必ず従ってください。
+【固定条件適用の絶対ルール】
+## 基本原則
+1. 指定されたテーブルを使用する場合、必ず対応する固定条件を適用する
+2. 固定条件は質問の内容に関わらず常に適用する
+3. 固定条件は変更・省略してはならない
+## 固定条件の定義方法
+各テーブルに対して以下の形式で固定条件を定義：
+【テーブル名】：物理テーブル名
+【適用タイミング】：WHERE句 / JOIN条件 / サブクエリ
+【固定条件】：必ず追加するSQL条件文
+【適用理由】：なぜこの条件が必要か（業務ルール説明）
+【例外】：条件を適用しないケース（ある場合のみ）
+## 固定条件の定義例
+### 定義例1：最新データか判別
+【テーブル名】：PS_Z_IF_HRBASE_VW（人事基本 ｸｴﾘﾋﾞｭｰ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."EFFDT" = (
+    SELECT MAX(h2."EFFDT")
+    FROM "PS_Z_IF_HRBASE_VW" t2
+    WHERE t2."EMPLID" = t1."EMPLID"
+    AND t2."EFFDT" &lt;= SYSDATE
+)
+【適用理由】：
+- 基準となる日付（SYSDATE）の当日を含めた最大の日付を取得する事でどの履歴データが基準日時点の最新データか判別します。
+【例外】：なし（常に適用）
+### 定義例2：HR ｽﾃｰﾀｽが有効レコードのみ取得
+【テーブル名】：PS_Z_IF_HRBASE_VW（人事基本 ｸｴﾘﾋﾞｭｰ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."HR_STATUS" = 'A'
+【適用理由】：
+- 有効レコードのみ取得
+【例外】：なし（常に適用）
+### 定義例3：EFF_STATUS（ｽﾃｰﾀｽ）が有効レコードのみ取得
+【テーブル名】：PS_Z_PUB_QLFCT_TBL（公的資格ﾏｽﾀ）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND t1."EFF_STATUS" = 'A'
+【適用理由】：
+- 有効レコードのみ取得
+【例外】：なし（常に適用）
+### 定義例4：公的資格取得補助が0のものは除外
+【テーブル名】：PS_Z_GP_WA_SAL_ER（別名 ZER）、PS_Z_GP_WA_RTRO（別名 ZRT）。
+【適用タイミング】：WHERE句
+【固定条件】：
+AND (ZER."Z_GP_ER6020" + ZER."Z_GP_ER6021" + ZRT."Z_GP_ER6020R") &lt;&gt; 0
+【適用理由】：
+- 公的資格取得補助が0のものは除外
+【例外】：なし（常に適用）
+### 定義例5："LOCATION" = '109'のレコードのみ取得
+【テーブル名】：PS_Z_IF_HRBASE_VW（別名 ZHR）。
+【適用タイミング】：WHERE句
+【固定条件】：
+AND ZHR."LOCATION" = '109'
+【適用理由】：
+- "LOCATION" = '109'のレコードのみ取得
+【例外】：なし（常に適用）
+### 定義例6：CAL_RUN_IDが最も新しいもの（CAL_RUN_ID = MAX(CAL_RUN_ID)）を取得
+【テーブル名】：PS_Z_GP_WA_SAL_ER（別名 ZER）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND ZER.CAL_RUN_ID = (
+　　SELECT MAX(ZER1.CAL_RUN_ID ) 
+    FROM PS_Z_GP_WA_SAL_ER ZER1
+    WHERE ZER1.EMPLID = ZER.EMPLID
+    AND ZER1.EMPL_RCD = ZER.EMPL_RCD
+    AND ZER1.CAL_ID = ZER.CAL_ID)
+【適用理由】：
+- CAL_RUN_IDが最も新しいもの（CAL_RUN_ID = MAX(CAL_RUN_ID)）を取得
+【例外】：なし（常に適用）
+### 定義例7：YYYY年MM月以降のレコードはSUBSTR関数を使用
+【テーブル名】：PS_Z_GP_WA_SAL_ER（別名 ZER）。
+【適用タイミング】：WHERE句
+【固定条件】：
+AND SUBSTR(ZER."CAL_ID", 4, 6) &gt;= 'YYYYMM'
+【適用理由】：
+- YYYY年MM月以降のレコードはSUBSTR関数を使用
+【例外】：なし（常に適用）
+### 定義例8：PS_Z_PUB_QLFCT_TBL（公的資格ﾏｽﾀ）のZ_PUBQLFGRANTS_TYPが「1:合格」、「2:合・不合格」の公的資格を取得した人が対象
+【テーブル名】：PS_Z_PUB_QLFCT_TBL（別名 ZPT）。
+【適用タイミング】：WHERE句
+【固定条件】：
+AND ZPT.Z_PUBQLFGRANTS_TYP IN ('1','2')
+【適用理由】：
+- PS_Z_PUB_QLFCT_TBL（公的資格ﾏｽﾀ）のZ_PUBQLFGRANTS_TYPが「1:合格」、「2:合・不合格」の公的資格を取得した人が対象
+【例外】：なし（常に適用）
+### 定義例9：PS_Z_IF_PUBQLF_VW（別名 ZPQ）のDT_ISSUEDに対して、YYYY年MM月DD日以降のレコードを取得する際はTO_DATEの関数を使用
+【テーブル名】：PS_Z_IF_PUBQLF_VW（別名 ZPQ）。
+【適用タイミング】：WHERE句
+【固定条件】：
+AND ZPQ.DT_ISSUED &gt;= TO_DATE('YYYY年MM月DD日','YYYY/MM/DD')
+【適用理由】：
+- YYYY年MM月DD日以降のレコードを取得する際はTO_DATEの関数を使用
+【例外】：なし（常に適用）
+### 定義例10：EFFDTが最も新しいもの（EFFDT = MAX(EFFDT)）を取得
+【テーブル名】：PS_Z_PUB_QLFCT_TBL（別名 ZPT）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND ZPT.EFFDT = (SELECT MAX(ZPT1.EFFDT)
+                                 FROM PS_Z_PUB_QLFCT_TBL ZPT1
+                              WHERE 1 = 1
+                                   AND ZPT1.SETID = ZPT.SETID
+                                   AND ZPT1.Z_PUBLIC_QLFCT_CD1 = ZPT.Z_PUBLIC_QLFCT_CD1
+                                   AND ZPT1.Z_PUBQLF_CLASS = ZPT.Z_PUBQLF_CLASS
+                                   AND ZPT1.Z_PUBLIC_QLFCT_CD3 = ZPT.Z_PUBLIC_QLFCT_CD3
+                                   AND ZPT1.EFFDT &lt;= SYSDATE)
+【適用理由】：
+- EFFDTが最も新しいもの（EFFDT = MAX(EFFDT)）を取得
+【例外】：なし（常に適用）
+### 定義例11：有効なEMPLIDのみ取得
+【テーブル名】：PS_Z_GP_WA_SAL_ER（別名 ZER）
+【適用タイミング】：WHERE句
+【固定条件】：
+AND EXISTS (SELECT 'x'
+                        FROM PS_Z_IF_PUBQLF_VW ZPQ
+                                 ,PS_Z_PUB_QLFCT_TBL ZPT
+                      WHERE ZPQ.EMPLID = ZER.EMPLID
+                           AND ZPT.Z_PUBLIC_QLFCT_CD = ZPQ.Z_PUBLIC_QLFCT_CD
+                           AND ZPT.EFFDT = (SELECT MAX(ZPT1.EFFDT)
+                                                            FROM PS_Z_PUB_QLFCT_TBL ZPT1
+                                                         WHERE 1 = 1
+                                                              AND ZPT1.SETID = ZPT.SETID
+                                                              AND ZPT1.Z_PUBLIC_QLFCT_CD1 = ZPT.Z_PUBLIC_QLFCT_CD1
+                                                              AND ZPT1.Z_PUBQLF_CLASS = ZPT.Z_PUBQLF_CLASS
+                                                              AND ZPT1.Z_PUBLIC_QLFCT_CD3 = ZPT.Z_PUBLIC_QLFCT_CD3
+                                                              AND ZPT1.EFFDT &lt;= SYSDATE)
+                          AND ZPQ.DT_ISSUED &gt;= TO_DATE('2025/04/01','YYYY/MM/DD')  -- 資格取得日が2025年4月以降
+                          AND ZPT.Z_PUBQLFGRANTS_TYP IN ('1','2') -- 1:合格、2:合格・不合格時に公的資格補助金が支給される資格
+                          )
+【適用理由】：
+- 有効なEMPLIDのみ取得
+【例外】：なし（常に適用）</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>